--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T17:27:39+00:00</t>
+    <t>2026-02-05T18:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T18:16:37+00:00</t>
+    <t>2026-02-06T16:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T16:44:46+00:00</t>
+    <t>2026-02-09T14:48:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T14:48:50+00:00</t>
+    <t>2026-02-13T15:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:04:48+00:00</t>
+    <t>2026-02-13T15:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:15:54+00:00</t>
+    <t>2026-02-13T15:40:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:40:14+00:00</t>
+    <t>2026-02-13T15:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:51:32+00:00</t>
+    <t>2026-02-17T13:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T13:15:51+00:00</t>
+    <t>2026-02-18T14:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T14:12:10+00:00</t>
+    <t>2026-02-18T14:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T14:26:16+00:00</t>
+    <t>2026-02-18T16:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T16:47:38+00:00</t>
+    <t>2026-02-19T09:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T09:13:17+00:00</t>
+    <t>2026-03-09T13:55:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-meta-creation-date.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:55:47+00:00</t>
+    <t>2026-03-09T14:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
